--- a/AAII_Financials/Yearly/LW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LW_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/LW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LW_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>LW</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45438</v>
+      </c>
+      <c r="E7" s="2">
         <v>45074</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44710</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44346</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43982</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43611</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43247</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42883</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42519</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42155</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41784</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41420</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41056</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6467600</v>
+      </c>
+      <c r="E8" s="3">
         <v>5350600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4098900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3670900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3792400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3756500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3423700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3168000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2993800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2925000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2815200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2778400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4700900</v>
+      </c>
+      <c r="E9" s="3">
         <v>3891500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3266900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2838900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2897200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2753000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2544200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4770700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6972800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4664100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2229500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2086700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1766700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1459100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>832000</v>
       </c>
       <c r="F10" s="3">
         <v>832000</v>
       </c>
       <c r="G10" s="3">
+        <v>832000</v>
+      </c>
+      <c r="H10" s="3">
         <v>895200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1003500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>879500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1602700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-3979000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1739100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>585700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>691700</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,29 +873,30 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E12" s="3">
         <v>17200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12900</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
         <v>15400</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,41 +960,44 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E14" s="3">
         <v>5200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>53300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>8700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
@@ -986,32 +1005,35 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>30700</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5402300</v>
+      </c>
+      <c r="E17" s="3">
         <v>4468500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3707800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3196100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3235500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3088100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2843600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2649700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2620500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2543600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2450700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2347400</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1065300</v>
+      </c>
+      <c r="E18" s="3">
         <v>882100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>391100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>474800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>556900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>668400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>580100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>518300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>373300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>381400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>364500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>431000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1178,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1173,191 +1206,206 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>5900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1372100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1104900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>583200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>663600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>740900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>830800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>723400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>627400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>475100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>483900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>442900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>506700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E22" s="3">
         <v>109200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>107700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>118300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>108000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>107100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>108800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>61200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>5300</v>
       </c>
       <c r="N22" s="3">
         <v>5300</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>929500</v>
+      </c>
+      <c r="E23" s="3">
         <v>772900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>283400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>356500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>448900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>561300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>471300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>457100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>367400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>375300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>358400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>423500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>253900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E24" s="3">
         <v>224600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>71800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>90500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>112300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>136000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>195000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>170200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>144500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>140400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>117700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>151900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>93800</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>699500</v>
+      </c>
+      <c r="E26" s="3">
         <v>548300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>211600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>266000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>336600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>425300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>276300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>286900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>222900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>234900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>240700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>271600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>725500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1008900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>200900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>317800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>365900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>465400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>340300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>324800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>280500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>266600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>260900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>298300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1538,18 +1598,18 @@
       <c r="F29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>2400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>73800</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,9 +1715,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1677,65 +1746,71 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>725500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1008900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>200900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>317800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>365900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>467800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>414100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>324800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>280500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>266600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>260900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>298300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>725500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1008900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>200900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>317800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>365900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>467800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>414100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>324800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>280500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>266600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>260900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>298300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45438</v>
+      </c>
+      <c r="E38" s="2">
         <v>45074</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44710</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44346</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43982</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43611</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43247</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42883</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42519</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42155</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41784</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41420</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41056</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E41" s="3">
         <v>304800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>525000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>783500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1364000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>57100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,204 +2073,219 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>743600</v>
+      </c>
+      <c r="E43" s="3">
         <v>724200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>447300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>366900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>342100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>340100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>225900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>185200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>186500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>171400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>167800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1138600</v>
+      </c>
+      <c r="E44" s="3">
         <v>932000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>574400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>513500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>486700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>498300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>549700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>525000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>498900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>488200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>440700</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E45" s="3">
         <v>166200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>112900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>117800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>110900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>99200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>90900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>58200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>61500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>89200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2090000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2127200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1659600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1781700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2302600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>961500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>930400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>858200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>780000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>751700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>724700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3">
         <v>43500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>257400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>310200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>250200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>224600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>219800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>178600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3715800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2954100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1698200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1665700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1702000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1597800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1420800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1271200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1043100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1001300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>926800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1164800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1150900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>351700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>371400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>342100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>243500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>170500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>170200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>173500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>176600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>153500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>396400</v>
+      </c>
+      <c r="E52" s="3">
         <v>244100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>172900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>80400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>65400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>162700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>126300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>125000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7367000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6519800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4139800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4209400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4662300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3048100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2752600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2485600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2159300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2055900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1930000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1866500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1767500</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>833800</v>
+      </c>
+      <c r="E57" s="3">
         <v>636600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>402600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>359300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>244400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>289200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>254400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>295000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>238000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>235900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>229200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>382700</v>
+      </c>
+      <c r="E58" s="3">
         <v>213800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>32200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>32000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>547500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>46400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>48300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>59900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>38400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>42700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>407600</v>
+      </c>
+      <c r="E59" s="3">
         <v>509800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>264300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>226900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>233000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>217200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>216000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>133200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>110600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>85300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1624100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1360200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>699100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>618200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1024900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>552800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>518700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>555400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>409600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>389200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>317400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3440700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3248400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2695800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2705400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2992600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2280200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2336700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2365000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>104600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>86500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>124300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>120500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>121400</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>514400</v>
+      </c>
+      <c r="E62" s="3">
         <v>499900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>384400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>405200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>404800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>219700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>176400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>161700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>197100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>181100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>181400</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5579200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5108500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3779300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3728800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4422300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3052700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3087400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3132800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>758700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>698400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>665000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,36 +3300,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2699800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2160700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1305500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1244600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1064600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>803600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>426400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>121000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3172,9 +3345,12 @@
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1787800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1411300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>360500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>480600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>240000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-334800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-647200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1400600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1357500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1265000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45438</v>
+      </c>
+      <c r="E80" s="2">
         <v>45074</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44710</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44346</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43982</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43611</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43247</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42883</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42519</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42155</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41784</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41420</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41056</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>725500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1008900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>200900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>317800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>365900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>467800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>414100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>324800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>280500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>266600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>260900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>298300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>306800</v>
+      </c>
+      <c r="E83" s="3">
         <v>222800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>192100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>188800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>184000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>162400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>143300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>109100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>95900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>96400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>79200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>798200</v>
+      </c>
+      <c r="E89" s="3">
         <v>761700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>418100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>553200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>574000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>680900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>481200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>446900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>382300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>353700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>386400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>302600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-991800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-736000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-306400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-163300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-208400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-334200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-306800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-287400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-152300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-114700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-194600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-112500</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-984100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1340900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-310500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-162500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-346000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-423000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-306800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-285300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-144300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-171200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-173200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-106400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,35 +4220,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-146100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-138400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-135300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-121300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-113300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-110200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-27400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E100" s="3">
         <v>340800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-363400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-974000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1125000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-299600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-178900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-142000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-232800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-177700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-199600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-203600</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>18200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-233400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-220200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-258500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-580500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1351800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LW_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>LW</t>
   </si>
@@ -771,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4700900</v>
+        <v>4680200</v>
       </c>
       <c r="E9" s="3">
         <v>3891500</v>
@@ -816,7 +816,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1766700</v>
+        <v>1787400</v>
       </c>
       <c r="E10" s="3">
         <v>1459100</v>
@@ -891,14 +891,14 @@
       <c r="G12" s="3">
         <v>12900</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
+      <c r="H12" s="3">
+        <v>15400</v>
       </c>
       <c r="I12" s="3">
         <v>15400</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
+      <c r="J12" s="3">
+        <v>13500</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
@@ -970,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>12800</v>
+        <v>33500</v>
       </c>
       <c r="E14" s="3">
         <v>5200</v>
@@ -978,14 +978,14 @@
       <c r="F14" s="3">
         <v>53300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="G14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>8700</v>
@@ -1017,23 +1017,23 @@
       <c r="D15" s="3">
         <v>30700</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
+      <c r="E15" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>12200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>181700</v>
+      </c>
+      <c r="H15" s="3">
+        <v>176100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>157700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>138700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5402300</v>
+        <v>5358200</v>
       </c>
       <c r="E17" s="3">
-        <v>4468500</v>
+        <v>4483000</v>
       </c>
       <c r="F17" s="3">
-        <v>3707800</v>
+        <v>3651200</v>
       </c>
       <c r="G17" s="3">
-        <v>3196100</v>
+        <v>3197400</v>
       </c>
       <c r="H17" s="3">
-        <v>3235500</v>
+        <v>3235400</v>
       </c>
       <c r="I17" s="3">
-        <v>3088100</v>
+        <v>3084800</v>
       </c>
       <c r="J17" s="3">
-        <v>2843600</v>
+        <v>2839600</v>
       </c>
       <c r="K17" s="3">
         <v>2649700</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1065300</v>
+        <v>1109400</v>
       </c>
       <c r="E18" s="3">
-        <v>882100</v>
+        <v>867600</v>
       </c>
       <c r="F18" s="3">
-        <v>391100</v>
+        <v>447700</v>
       </c>
       <c r="G18" s="3">
-        <v>474800</v>
+        <v>473500</v>
       </c>
       <c r="H18" s="3">
-        <v>556900</v>
+        <v>557000</v>
       </c>
       <c r="I18" s="3">
-        <v>668400</v>
+        <v>671700</v>
       </c>
       <c r="J18" s="3">
-        <v>580100</v>
+        <v>584100</v>
       </c>
       <c r="K18" s="3">
         <v>518300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-15400</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-480300</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-53100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-29200</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-56200</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-88300</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1372100</v>
+        <v>1155500</v>
       </c>
       <c r="E21" s="3">
-        <v>1104900</v>
+        <v>1363000</v>
       </c>
       <c r="F21" s="3">
-        <v>583200</v>
+        <v>445900</v>
       </c>
       <c r="G21" s="3">
-        <v>663600</v>
+        <v>708300</v>
       </c>
       <c r="H21" s="3">
-        <v>740900</v>
+        <v>762300</v>
       </c>
       <c r="I21" s="3">
-        <v>830800</v>
+        <v>885600</v>
       </c>
       <c r="J21" s="3">
-        <v>723400</v>
+        <v>811100</v>
       </c>
       <c r="K21" s="3">
         <v>627400</v>
@@ -1284,10 +1284,10 @@
         <v>107700</v>
       </c>
       <c r="G22" s="3">
-        <v>118300</v>
+        <v>117300</v>
       </c>
       <c r="H22" s="3">
-        <v>108000</v>
+        <v>106300</v>
       </c>
       <c r="I22" s="3">
         <v>107100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>929500</v>
+        <v>955500</v>
       </c>
       <c r="E23" s="3">
-        <v>772900</v>
+        <v>1233500</v>
       </c>
       <c r="F23" s="3">
-        <v>283400</v>
+        <v>272700</v>
       </c>
       <c r="G23" s="3">
-        <v>356500</v>
+        <v>408300</v>
       </c>
       <c r="H23" s="3">
-        <v>448900</v>
+        <v>478200</v>
       </c>
       <c r="I23" s="3">
-        <v>561300</v>
+        <v>620800</v>
       </c>
       <c r="J23" s="3">
-        <v>471300</v>
+        <v>554900</v>
       </c>
       <c r="K23" s="3">
         <v>457100</v>
@@ -1380,10 +1380,10 @@
         <v>112300</v>
       </c>
       <c r="I24" s="3">
-        <v>136000</v>
+        <v>133600</v>
       </c>
       <c r="J24" s="3">
-        <v>195000</v>
+        <v>121200</v>
       </c>
       <c r="K24" s="3">
         <v>170200</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>699500</v>
+        <v>725500</v>
       </c>
       <c r="E26" s="3">
-        <v>548300</v>
+        <v>1008900</v>
       </c>
       <c r="F26" s="3">
-        <v>211600</v>
+        <v>200900</v>
       </c>
       <c r="G26" s="3">
-        <v>266000</v>
+        <v>317800</v>
       </c>
       <c r="H26" s="3">
-        <v>336600</v>
+        <v>365900</v>
       </c>
       <c r="I26" s="3">
-        <v>425300</v>
+        <v>487200</v>
       </c>
       <c r="J26" s="3">
-        <v>276300</v>
+        <v>433700</v>
       </c>
       <c r="K26" s="3">
         <v>286900</v>
@@ -1515,10 +1515,10 @@
         <v>365900</v>
       </c>
       <c r="I27" s="3">
-        <v>465400</v>
+        <v>467800</v>
       </c>
       <c r="J27" s="3">
-        <v>340300</v>
+        <v>414100</v>
       </c>
       <c r="K27" s="3">
         <v>324800</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>73800</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>4</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>480300</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>53100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>29200</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>56200</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>88300</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         <v>365900</v>
       </c>
       <c r="I33" s="3">
-        <v>467800</v>
+        <v>478600</v>
       </c>
       <c r="J33" s="3">
-        <v>414100</v>
+        <v>416800</v>
       </c>
       <c r="K33" s="3">
         <v>324800</v>
@@ -1875,10 +1875,10 @@
         <v>365900</v>
       </c>
       <c r="I35" s="3">
-        <v>467800</v>
+        <v>478600</v>
       </c>
       <c r="J35" s="3">
-        <v>414100</v>
+        <v>416800</v>
       </c>
       <c r="K35" s="3">
         <v>324800</v>
@@ -2128,13 +2128,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1138600</v>
+        <v>1178900</v>
       </c>
       <c r="E44" s="3">
-        <v>932000</v>
+        <v>954500</v>
       </c>
       <c r="F44" s="3">
-        <v>574400</v>
+        <v>602500</v>
       </c>
       <c r="G44" s="3">
         <v>513500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>136400</v>
+        <v>1400</v>
       </c>
       <c r="E45" s="3">
-        <v>166200</v>
+        <v>3000</v>
       </c>
       <c r="F45" s="3">
-        <v>112900</v>
+        <v>7000</v>
       </c>
       <c r="G45" s="3">
-        <v>117800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>109800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>110900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>99200</v>
+        <v>15300</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>90900</v>
@@ -2265,8 +2265,8 @@
       <c r="D47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="3">
-        <v>43500</v>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F47" s="3">
         <v>257400</v>
@@ -2353,13 +2353,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1164800</v>
+        <v>1392700</v>
       </c>
       <c r="E49" s="3">
-        <v>1150900</v>
+        <v>1326300</v>
       </c>
       <c r="F49" s="3">
-        <v>351700</v>
+        <v>421300</v>
       </c>
       <c r="G49" s="3">
         <v>371400</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>396400</v>
+        <v>155400</v>
       </c>
       <c r="E52" s="3">
-        <v>244100</v>
+        <v>106400</v>
       </c>
       <c r="F52" s="3">
-        <v>172900</v>
+        <v>97300</v>
       </c>
       <c r="G52" s="3">
-        <v>80400</v>
+        <v>78200</v>
       </c>
       <c r="H52" s="3">
-        <v>65400</v>
+        <v>63100</v>
       </c>
       <c r="I52" s="3">
-        <v>20700</v>
+        <v>18900</v>
       </c>
       <c r="J52" s="3">
-        <v>11100</v>
+        <v>10700</v>
       </c>
       <c r="K52" s="3">
         <v>7400</v>
@@ -2706,19 +2706,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>382700</v>
+        <v>412000</v>
       </c>
       <c r="E58" s="3">
-        <v>213800</v>
+        <v>242300</v>
       </c>
       <c r="F58" s="3">
-        <v>32200</v>
+        <v>54600</v>
       </c>
       <c r="G58" s="3">
-        <v>32000</v>
+        <v>61100</v>
       </c>
       <c r="H58" s="3">
-        <v>547500</v>
+        <v>575900</v>
       </c>
       <c r="I58" s="3">
         <v>46400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>407600</v>
+        <v>101100</v>
       </c>
       <c r="E59" s="3">
-        <v>509800</v>
+        <v>115900</v>
       </c>
       <c r="F59" s="3">
-        <v>264300</v>
+        <v>47400</v>
       </c>
       <c r="G59" s="3">
-        <v>226900</v>
+        <v>34400</v>
       </c>
       <c r="H59" s="3">
-        <v>233000</v>
+        <v>34900</v>
       </c>
       <c r="I59" s="3">
-        <v>217200</v>
+        <v>29700</v>
       </c>
       <c r="J59" s="3">
-        <v>216000</v>
+        <v>31100</v>
       </c>
       <c r="K59" s="3">
         <v>200500</v>
@@ -2841,19 +2841,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3440700</v>
+        <v>3556100</v>
       </c>
       <c r="E61" s="3">
-        <v>3248400</v>
+        <v>3375900</v>
       </c>
       <c r="F61" s="3">
-        <v>2695800</v>
+        <v>2800500</v>
       </c>
       <c r="G61" s="3">
-        <v>2705400</v>
+        <v>2825700</v>
       </c>
       <c r="H61" s="3">
-        <v>2992600</v>
+        <v>3137200</v>
       </c>
       <c r="I61" s="3">
         <v>2280200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>514400</v>
+        <v>129000</v>
       </c>
       <c r="E62" s="3">
-        <v>499900</v>
+        <v>106700</v>
       </c>
       <c r="F62" s="3">
-        <v>384400</v>
+        <v>90700</v>
       </c>
       <c r="G62" s="3">
-        <v>405200</v>
+        <v>105600</v>
       </c>
       <c r="H62" s="3">
-        <v>404800</v>
+        <v>91300</v>
       </c>
       <c r="I62" s="3">
-        <v>219700</v>
+        <v>76700</v>
       </c>
       <c r="J62" s="3">
-        <v>176400</v>
+        <v>84300</v>
       </c>
       <c r="K62" s="3">
         <v>161700</v>
@@ -3084,7 +3084,7 @@
         <v>3052700</v>
       </c>
       <c r="J66" s="3">
-        <v>3087400</v>
+        <v>3031800</v>
       </c>
       <c r="K66" s="3">
         <v>3132800</v>
@@ -3645,10 +3645,10 @@
         <v>365900</v>
       </c>
       <c r="I81" s="3">
-        <v>467800</v>
+        <v>478600</v>
       </c>
       <c r="J81" s="3">
-        <v>414100</v>
+        <v>416800</v>
       </c>
       <c r="K81" s="3">
         <v>324800</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>306800</v>
+        <v>282700</v>
       </c>
       <c r="E83" s="3">
-        <v>222800</v>
+        <v>211700</v>
       </c>
       <c r="F83" s="3">
-        <v>192100</v>
+        <v>181500</v>
       </c>
       <c r="G83" s="3">
-        <v>188800</v>
+        <v>176700</v>
       </c>
       <c r="H83" s="3">
-        <v>184000</v>
+        <v>173600</v>
       </c>
       <c r="I83" s="3">
-        <v>162400</v>
+        <v>155500</v>
       </c>
       <c r="J83" s="3">
-        <v>143300</v>
+        <v>136300</v>
       </c>
       <c r="K83" s="3">
         <v>109100</v>
@@ -3970,10 +3970,10 @@
         <v>761700</v>
       </c>
       <c r="F89" s="3">
-        <v>418100</v>
+        <v>418600</v>
       </c>
       <c r="G89" s="3">
-        <v>553200</v>
+        <v>552700</v>
       </c>
       <c r="H89" s="3">
         <v>574000</v>
@@ -4028,19 +4028,19 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-991800</v>
+        <v>-929500</v>
       </c>
       <c r="E91" s="3">
-        <v>-736000</v>
+        <v>-654000</v>
       </c>
       <c r="F91" s="3">
-        <v>-306400</v>
+        <v>-290100</v>
       </c>
       <c r="G91" s="3">
-        <v>-163300</v>
+        <v>-147200</v>
       </c>
       <c r="H91" s="3">
-        <v>-208400</v>
+        <v>-167700</v>
       </c>
       <c r="I91" s="3">
         <v>-334200</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-174000</v>
+        <v>174000</v>
       </c>
       <c r="E96" s="3">
-        <v>-146100</v>
+        <v>146100</v>
       </c>
       <c r="F96" s="3">
-        <v>-138400</v>
+        <v>138400</v>
       </c>
       <c r="G96" s="3">
-        <v>-135300</v>
+        <v>135300</v>
       </c>
       <c r="H96" s="3">
-        <v>-121300</v>
+        <v>121300</v>
       </c>
       <c r="I96" s="3">
-        <v>-113300</v>
+        <v>113300</v>
       </c>
       <c r="J96" s="3">
-        <v>-110200</v>
+        <v>110200</v>
       </c>
       <c r="K96" s="3">
         <v>-27400</v>
@@ -4458,10 +4458,10 @@
         <v>18200</v>
       </c>
       <c r="F101" s="3">
-        <v>-2700</v>
+        <v>-3200</v>
       </c>
       <c r="G101" s="3">
-        <v>2800</v>
+        <v>3300</v>
       </c>
       <c r="H101" s="3">
         <v>-1200</v>

--- a/AAII_Financials/Yearly/LW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LW_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>LW</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45802</v>
+      </c>
+      <c r="E7" s="2">
         <v>45438</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45074</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44710</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44346</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43982</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43611</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43247</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42883</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42519</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42155</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41784</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41420</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41056</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6451300</v>
+      </c>
+      <c r="E8" s="3">
         <v>6467600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5350600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4098900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3670900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3792400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3756500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3423700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3168000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2993800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2925000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2815200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2778400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4977400</v>
+      </c>
+      <c r="E9" s="3">
         <v>4680200</v>
       </c>
-      <c r="E9" s="3">
-        <v>3891500</v>
-      </c>
       <c r="F9" s="3">
+        <v>3918500</v>
+      </c>
+      <c r="G9" s="3">
         <v>3266900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2838900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2897200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2753000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2544200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4770700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6972800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4664100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2229500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2086700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1473900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1787400</v>
       </c>
-      <c r="E10" s="3">
-        <v>1459100</v>
-      </c>
       <c r="F10" s="3">
-        <v>832000</v>
+        <v>1432100</v>
       </c>
       <c r="G10" s="3">
         <v>832000</v>
       </c>
       <c r="H10" s="3">
+        <v>832000</v>
+      </c>
+      <c r="I10" s="3">
         <v>895200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1003500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>879500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1602700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-3979000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1739100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>585700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>691700</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,35 +886,36 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E12" s="3">
         <v>26400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12900</v>
-      </c>
-      <c r="H12" s="3">
-        <v>15400</v>
       </c>
       <c r="I12" s="3">
         <v>15400</v>
       </c>
       <c r="J12" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K12" s="3">
         <v>13500</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,44 +979,47 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>175300</v>
+      </c>
+      <c r="E14" s="3">
         <v>33500</v>
       </c>
-      <c r="E14" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>53300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>8700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>26500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
@@ -1008,36 +1027,39 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>30700</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="3">
-        <v>15100</v>
+        <v>12100</v>
       </c>
       <c r="F15" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G15" s="3">
         <v>12200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>181700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>176100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>157700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>138700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5358200</v>
+        <v>5595700</v>
       </c>
       <c r="E17" s="3">
-        <v>4483000</v>
+        <v>5340200</v>
       </c>
       <c r="F17" s="3">
+        <v>4488200</v>
+      </c>
+      <c r="G17" s="3">
         <v>3651200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3197400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3235400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3084800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2839600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2649700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2620500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2543600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2450700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2347400</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1109400</v>
+        <v>855600</v>
       </c>
       <c r="E18" s="3">
-        <v>867600</v>
+        <v>1127400</v>
       </c>
       <c r="F18" s="3">
+        <v>862400</v>
+      </c>
+      <c r="G18" s="3">
         <v>447700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>473500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>557000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>671700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>584100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>518300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>373300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>381400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>364500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>431000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-15400</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-480300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-53100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-56200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-88300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>5900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1155500</v>
+        <v>870600</v>
       </c>
       <c r="E21" s="3">
-        <v>1363000</v>
+        <v>1136900</v>
       </c>
       <c r="F21" s="3">
+        <v>1351800</v>
+      </c>
+      <c r="G21" s="3">
         <v>445900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>708300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>762300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>885600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>811100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>627400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>475100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>483900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>442900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>506700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E22" s="3">
         <v>135800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>109200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>107700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>117300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>106300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>107100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>108800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>61200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>5300</v>
       </c>
       <c r="O22" s="3">
         <v>5300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500300</v>
+      </c>
+      <c r="E23" s="3">
         <v>955500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1233500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>272700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>408300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>478200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>620800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>554900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>457100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>367400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>375300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>358400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>423500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>253900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>143100</v>
+      </c>
+      <c r="E24" s="3">
         <v>230000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>224600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>71800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>90500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>112300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>133600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>121200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>170200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>144500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>140400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>117700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>151900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>93800</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>357200</v>
+      </c>
+      <c r="E26" s="3">
         <v>725500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1008900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>317800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>365900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>487200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>433700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>286900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>222900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>234900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>240700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>271600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>357200</v>
+      </c>
+      <c r="E27" s="3">
         <v>725500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1008900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>317800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>365900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>467800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>414100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>324800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>280500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>266600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>260900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>298300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,8 +1670,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>4</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>480300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>53100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>56200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>88300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>357200</v>
+      </c>
+      <c r="E33" s="3">
         <v>725500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1008900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>317800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>365900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>478600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>416800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>324800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>280500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>266600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>260900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>298300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>357200</v>
+      </c>
+      <c r="E35" s="3">
         <v>725500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1008900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>317800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>365900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>478600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>416800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>324800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>280500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>266600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>260900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>298300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45802</v>
+      </c>
+      <c r="E38" s="2">
         <v>45438</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45074</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44710</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44346</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43982</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43611</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43247</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42883</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42519</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42155</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41784</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41420</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41056</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E41" s="3">
         <v>71400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>304800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>525000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>783500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1364000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,189 +2165,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>781600</v>
+      </c>
+      <c r="E43" s="3">
         <v>743600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>724200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>447300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>366900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>342100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>340100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>225900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>185200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>186500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>171400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>167800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1070200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1178900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>954500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>602500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>513500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>486700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>498300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>549700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>525000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>498900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>488200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>440700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>90900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>58200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>61500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>89200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2032700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2090000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2127200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1659600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1781700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2302600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>961500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>930400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>858200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>780000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>751700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>724700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2268,27 +2372,27 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3">
         <v>257400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>310200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>250200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>224600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>219800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>178600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3801100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3715800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2954100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1698200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1665700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1702000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1597800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1420800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1271200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1043100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1001300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>926800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1412900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1392700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1326300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>421300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>371400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>342100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>243500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>170500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>170200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>173500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>176600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>153500</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E52" s="3">
         <v>155400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>106400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>97300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>78200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>162700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>126300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>125000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7392600</v>
+      </c>
+      <c r="E54" s="3">
         <v>7367000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6519800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4139800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4209400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4662300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3048100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2752600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2485600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2159300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2055900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1930000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1866500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1767500</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>616400</v>
+      </c>
+      <c r="E57" s="3">
         <v>833800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>636600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>402600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>359300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>244400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>289200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>254400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>295000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>238000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>235900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>229200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>472500</v>
+      </c>
+      <c r="E58" s="3">
         <v>412000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>242300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>54600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>575900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>38400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E59" s="3">
         <v>101100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>115900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>133200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>110600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>85300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1476000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1624100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1360200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>699100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>618200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1024900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>552800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>518700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>555400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>409600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>389200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>317400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3781700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3556100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3375900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2800500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2825700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3137200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2280200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2336700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2365000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>104600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>86500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>124300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>120500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>121400</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>129000</v>
+        <v>143700</v>
       </c>
       <c r="E62" s="3">
+        <v>142800</v>
+      </c>
+      <c r="F62" s="3">
         <v>106700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>90700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>105600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>91300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>76700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>84300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>161700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>197100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>181100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>181400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5654900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5579200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5108500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3779300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3728800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4422300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3052700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3031800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3132800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>758700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>698400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>665000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,39 +3473,42 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2848900</v>
+      </c>
+      <c r="E72" s="3">
         <v>2699800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2160700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1305500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1244600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1064600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>803600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>426400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>121000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3348,9 +3521,12 @@
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1737700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1787800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1411300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>360500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>480600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>240000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-334800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-647200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1400600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1357500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1265000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45802</v>
+      </c>
+      <c r="E80" s="2">
         <v>45438</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45074</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44710</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44346</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43982</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43611</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43247</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42883</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42519</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42155</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41784</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41420</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41056</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>357200</v>
+      </c>
+      <c r="E81" s="3">
         <v>725500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1008900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>317800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>365900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>478600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>416800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>324800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>280500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>266600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>260900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>298300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>371300</v>
+      </c>
+      <c r="E83" s="3">
         <v>282700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>211700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>181500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>176700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>173600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>155500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>136300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>109100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>95900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>96400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>77900</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>868300</v>
+      </c>
+      <c r="E89" s="3">
         <v>798200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>761700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>418600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>552700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>574000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>680900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>481200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>446900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>382300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>353700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>386400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>302600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-638200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-929500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-654000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-290100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-147200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-167700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-334200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-306800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-287400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-152300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-114700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-194600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-112500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-648000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-984100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1340900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-310500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-162500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-346000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-423000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-306800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-285300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-144300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-171200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-173200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-106400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,38 +4453,39 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E96" s="3">
         <v>174000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>146100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>138400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>135300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>121300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>113300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>110200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-27400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-225000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-48000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>340800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-363400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-974000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1125000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-299600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-178900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-142000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-232800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-177700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-199600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-203600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>18200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-233400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-220200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-258500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-580500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1351800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
